--- a/public/rent-assessment-template.xlsx
+++ b/public/rent-assessment-template.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R202"/>
+  <dimension ref="A1:T202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -500,10 +500,12 @@
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="24" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -572,27 +574,37 @@
           <t>ローン事務手数料</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>登記費用</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>保証月額家賃</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>管理費・修繕積立金(月額)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>固定資産税・都市計画税(年額)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>現在年齢</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>試算期間(年)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>所得税率(%)</t>
         </is>
@@ -647,18 +659,24 @@
         <v>110000</v>
       </c>
       <c r="N2" s="4" t="n">
+        <v>250000</v>
+      </c>
+      <c r="O2" s="4" t="n">
         <v>95000</v>
       </c>
-      <c r="O2" s="4" t="n">
+      <c r="P2" s="4" t="n">
         <v>15000</v>
       </c>
-      <c r="P2" s="4" t="n">
+      <c r="Q2" s="4" t="n">
         <v>80000</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="R2" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="R2" s="3" t="n">
+      <c r="S2" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T2" s="3" t="n">
         <v>33</v>
       </c>
     </row>
@@ -679,8 +697,10 @@
       <c r="N3" s="7" t="n"/>
       <c r="O3" s="7" t="n"/>
       <c r="P3" s="7" t="n"/>
-      <c r="Q3" s="6" t="n"/>
+      <c r="Q3" s="7" t="n"/>
       <c r="R3" s="6" t="n"/>
+      <c r="S3" s="6" t="n"/>
+      <c r="T3" s="6" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="n"/>
@@ -699,8 +719,10 @@
       <c r="N4" s="7" t="n"/>
       <c r="O4" s="7" t="n"/>
       <c r="P4" s="7" t="n"/>
-      <c r="Q4" s="6" t="n"/>
+      <c r="Q4" s="7" t="n"/>
       <c r="R4" s="6" t="n"/>
+      <c r="S4" s="6" t="n"/>
+      <c r="T4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -719,8 +741,10 @@
       <c r="N5" s="7" t="n"/>
       <c r="O5" s="7" t="n"/>
       <c r="P5" s="7" t="n"/>
-      <c r="Q5" s="6" t="n"/>
+      <c r="Q5" s="7" t="n"/>
       <c r="R5" s="6" t="n"/>
+      <c r="S5" s="6" t="n"/>
+      <c r="T5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n"/>
@@ -739,8 +763,10 @@
       <c r="N6" s="7" t="n"/>
       <c r="O6" s="7" t="n"/>
       <c r="P6" s="7" t="n"/>
-      <c r="Q6" s="6" t="n"/>
+      <c r="Q6" s="7" t="n"/>
       <c r="R6" s="6" t="n"/>
+      <c r="S6" s="6" t="n"/>
+      <c r="T6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n"/>
@@ -759,8 +785,10 @@
       <c r="N7" s="7" t="n"/>
       <c r="O7" s="7" t="n"/>
       <c r="P7" s="7" t="n"/>
-      <c r="Q7" s="6" t="n"/>
+      <c r="Q7" s="7" t="n"/>
       <c r="R7" s="6" t="n"/>
+      <c r="S7" s="6" t="n"/>
+      <c r="T7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n"/>
@@ -779,8 +807,10 @@
       <c r="N8" s="7" t="n"/>
       <c r="O8" s="7" t="n"/>
       <c r="P8" s="7" t="n"/>
-      <c r="Q8" s="6" t="n"/>
+      <c r="Q8" s="7" t="n"/>
       <c r="R8" s="6" t="n"/>
+      <c r="S8" s="6" t="n"/>
+      <c r="T8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -799,8 +829,10 @@
       <c r="N9" s="7" t="n"/>
       <c r="O9" s="7" t="n"/>
       <c r="P9" s="7" t="n"/>
-      <c r="Q9" s="6" t="n"/>
+      <c r="Q9" s="7" t="n"/>
       <c r="R9" s="6" t="n"/>
+      <c r="S9" s="6" t="n"/>
+      <c r="T9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -819,8 +851,10 @@
       <c r="N10" s="7" t="n"/>
       <c r="O10" s="7" t="n"/>
       <c r="P10" s="7" t="n"/>
-      <c r="Q10" s="6" t="n"/>
+      <c r="Q10" s="7" t="n"/>
       <c r="R10" s="6" t="n"/>
+      <c r="S10" s="6" t="n"/>
+      <c r="T10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
@@ -839,8 +873,10 @@
       <c r="N11" s="7" t="n"/>
       <c r="O11" s="7" t="n"/>
       <c r="P11" s="7" t="n"/>
-      <c r="Q11" s="6" t="n"/>
+      <c r="Q11" s="7" t="n"/>
       <c r="R11" s="6" t="n"/>
+      <c r="S11" s="6" t="n"/>
+      <c r="T11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
@@ -859,8 +895,10 @@
       <c r="N12" s="7" t="n"/>
       <c r="O12" s="7" t="n"/>
       <c r="P12" s="7" t="n"/>
-      <c r="Q12" s="6" t="n"/>
+      <c r="Q12" s="7" t="n"/>
       <c r="R12" s="6" t="n"/>
+      <c r="S12" s="6" t="n"/>
+      <c r="T12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -879,8 +917,10 @@
       <c r="N13" s="7" t="n"/>
       <c r="O13" s="7" t="n"/>
       <c r="P13" s="7" t="n"/>
-      <c r="Q13" s="6" t="n"/>
+      <c r="Q13" s="7" t="n"/>
       <c r="R13" s="6" t="n"/>
+      <c r="S13" s="6" t="n"/>
+      <c r="T13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -899,8 +939,10 @@
       <c r="N14" s="7" t="n"/>
       <c r="O14" s="7" t="n"/>
       <c r="P14" s="7" t="n"/>
-      <c r="Q14" s="6" t="n"/>
+      <c r="Q14" s="7" t="n"/>
       <c r="R14" s="6" t="n"/>
+      <c r="S14" s="6" t="n"/>
+      <c r="T14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
@@ -919,8 +961,10 @@
       <c r="N15" s="7" t="n"/>
       <c r="O15" s="7" t="n"/>
       <c r="P15" s="7" t="n"/>
-      <c r="Q15" s="6" t="n"/>
+      <c r="Q15" s="7" t="n"/>
       <c r="R15" s="6" t="n"/>
+      <c r="S15" s="6" t="n"/>
+      <c r="T15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
@@ -939,8 +983,10 @@
       <c r="N16" s="7" t="n"/>
       <c r="O16" s="7" t="n"/>
       <c r="P16" s="7" t="n"/>
-      <c r="Q16" s="6" t="n"/>
+      <c r="Q16" s="7" t="n"/>
       <c r="R16" s="6" t="n"/>
+      <c r="S16" s="6" t="n"/>
+      <c r="T16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -959,8 +1005,10 @@
       <c r="N17" s="7" t="n"/>
       <c r="O17" s="7" t="n"/>
       <c r="P17" s="7" t="n"/>
-      <c r="Q17" s="6" t="n"/>
+      <c r="Q17" s="7" t="n"/>
       <c r="R17" s="6" t="n"/>
+      <c r="S17" s="6" t="n"/>
+      <c r="T17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -979,8 +1027,10 @@
       <c r="N18" s="7" t="n"/>
       <c r="O18" s="7" t="n"/>
       <c r="P18" s="7" t="n"/>
-      <c r="Q18" s="6" t="n"/>
+      <c r="Q18" s="7" t="n"/>
       <c r="R18" s="6" t="n"/>
+      <c r="S18" s="6" t="n"/>
+      <c r="T18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
@@ -999,8 +1049,10 @@
       <c r="N19" s="7" t="n"/>
       <c r="O19" s="7" t="n"/>
       <c r="P19" s="7" t="n"/>
-      <c r="Q19" s="6" t="n"/>
+      <c r="Q19" s="7" t="n"/>
       <c r="R19" s="6" t="n"/>
+      <c r="S19" s="6" t="n"/>
+      <c r="T19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
@@ -1019,8 +1071,10 @@
       <c r="N20" s="7" t="n"/>
       <c r="O20" s="7" t="n"/>
       <c r="P20" s="7" t="n"/>
-      <c r="Q20" s="6" t="n"/>
+      <c r="Q20" s="7" t="n"/>
       <c r="R20" s="6" t="n"/>
+      <c r="S20" s="6" t="n"/>
+      <c r="T20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -1039,8 +1093,10 @@
       <c r="N21" s="7" t="n"/>
       <c r="O21" s="7" t="n"/>
       <c r="P21" s="7" t="n"/>
-      <c r="Q21" s="6" t="n"/>
+      <c r="Q21" s="7" t="n"/>
       <c r="R21" s="6" t="n"/>
+      <c r="S21" s="6" t="n"/>
+      <c r="T21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
@@ -1059,8 +1115,10 @@
       <c r="N22" s="7" t="n"/>
       <c r="O22" s="7" t="n"/>
       <c r="P22" s="7" t="n"/>
-      <c r="Q22" s="6" t="n"/>
+      <c r="Q22" s="7" t="n"/>
       <c r="R22" s="6" t="n"/>
+      <c r="S22" s="6" t="n"/>
+      <c r="T22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
@@ -1079,8 +1137,10 @@
       <c r="N23" s="7" t="n"/>
       <c r="O23" s="7" t="n"/>
       <c r="P23" s="7" t="n"/>
-      <c r="Q23" s="6" t="n"/>
+      <c r="Q23" s="7" t="n"/>
       <c r="R23" s="6" t="n"/>
+      <c r="S23" s="6" t="n"/>
+      <c r="T23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
@@ -1099,8 +1159,10 @@
       <c r="N24" s="7" t="n"/>
       <c r="O24" s="7" t="n"/>
       <c r="P24" s="7" t="n"/>
-      <c r="Q24" s="6" t="n"/>
+      <c r="Q24" s="7" t="n"/>
       <c r="R24" s="6" t="n"/>
+      <c r="S24" s="6" t="n"/>
+      <c r="T24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -1119,8 +1181,10 @@
       <c r="N25" s="7" t="n"/>
       <c r="O25" s="7" t="n"/>
       <c r="P25" s="7" t="n"/>
-      <c r="Q25" s="6" t="n"/>
+      <c r="Q25" s="7" t="n"/>
       <c r="R25" s="6" t="n"/>
+      <c r="S25" s="6" t="n"/>
+      <c r="T25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
@@ -1139,8 +1203,10 @@
       <c r="N26" s="7" t="n"/>
       <c r="O26" s="7" t="n"/>
       <c r="P26" s="7" t="n"/>
-      <c r="Q26" s="6" t="n"/>
+      <c r="Q26" s="7" t="n"/>
       <c r="R26" s="6" t="n"/>
+      <c r="S26" s="6" t="n"/>
+      <c r="T26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
@@ -1159,8 +1225,10 @@
       <c r="N27" s="7" t="n"/>
       <c r="O27" s="7" t="n"/>
       <c r="P27" s="7" t="n"/>
-      <c r="Q27" s="6" t="n"/>
+      <c r="Q27" s="7" t="n"/>
       <c r="R27" s="6" t="n"/>
+      <c r="S27" s="6" t="n"/>
+      <c r="T27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
@@ -1179,8 +1247,10 @@
       <c r="N28" s="7" t="n"/>
       <c r="O28" s="7" t="n"/>
       <c r="P28" s="7" t="n"/>
-      <c r="Q28" s="6" t="n"/>
+      <c r="Q28" s="7" t="n"/>
       <c r="R28" s="6" t="n"/>
+      <c r="S28" s="6" t="n"/>
+      <c r="T28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -1199,8 +1269,10 @@
       <c r="N29" s="7" t="n"/>
       <c r="O29" s="7" t="n"/>
       <c r="P29" s="7" t="n"/>
-      <c r="Q29" s="6" t="n"/>
+      <c r="Q29" s="7" t="n"/>
       <c r="R29" s="6" t="n"/>
+      <c r="S29" s="6" t="n"/>
+      <c r="T29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
@@ -1219,8 +1291,10 @@
       <c r="N30" s="7" t="n"/>
       <c r="O30" s="7" t="n"/>
       <c r="P30" s="7" t="n"/>
-      <c r="Q30" s="6" t="n"/>
+      <c r="Q30" s="7" t="n"/>
       <c r="R30" s="6" t="n"/>
+      <c r="S30" s="6" t="n"/>
+      <c r="T30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
@@ -1239,8 +1313,10 @@
       <c r="N31" s="7" t="n"/>
       <c r="O31" s="7" t="n"/>
       <c r="P31" s="7" t="n"/>
-      <c r="Q31" s="6" t="n"/>
+      <c r="Q31" s="7" t="n"/>
       <c r="R31" s="6" t="n"/>
+      <c r="S31" s="6" t="n"/>
+      <c r="T31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -1259,8 +1335,10 @@
       <c r="N32" s="7" t="n"/>
       <c r="O32" s="7" t="n"/>
       <c r="P32" s="7" t="n"/>
-      <c r="Q32" s="6" t="n"/>
+      <c r="Q32" s="7" t="n"/>
       <c r="R32" s="6" t="n"/>
+      <c r="S32" s="6" t="n"/>
+      <c r="T32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -1279,8 +1357,10 @@
       <c r="N33" s="7" t="n"/>
       <c r="O33" s="7" t="n"/>
       <c r="P33" s="7" t="n"/>
-      <c r="Q33" s="6" t="n"/>
+      <c r="Q33" s="7" t="n"/>
       <c r="R33" s="6" t="n"/>
+      <c r="S33" s="6" t="n"/>
+      <c r="T33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
@@ -1299,8 +1379,10 @@
       <c r="N34" s="7" t="n"/>
       <c r="O34" s="7" t="n"/>
       <c r="P34" s="7" t="n"/>
-      <c r="Q34" s="6" t="n"/>
+      <c r="Q34" s="7" t="n"/>
       <c r="R34" s="6" t="n"/>
+      <c r="S34" s="6" t="n"/>
+      <c r="T34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
@@ -1319,8 +1401,10 @@
       <c r="N35" s="7" t="n"/>
       <c r="O35" s="7" t="n"/>
       <c r="P35" s="7" t="n"/>
-      <c r="Q35" s="6" t="n"/>
+      <c r="Q35" s="7" t="n"/>
       <c r="R35" s="6" t="n"/>
+      <c r="S35" s="6" t="n"/>
+      <c r="T35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -1339,8 +1423,10 @@
       <c r="N36" s="7" t="n"/>
       <c r="O36" s="7" t="n"/>
       <c r="P36" s="7" t="n"/>
-      <c r="Q36" s="6" t="n"/>
+      <c r="Q36" s="7" t="n"/>
       <c r="R36" s="6" t="n"/>
+      <c r="S36" s="6" t="n"/>
+      <c r="T36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
@@ -1359,8 +1445,10 @@
       <c r="N37" s="7" t="n"/>
       <c r="O37" s="7" t="n"/>
       <c r="P37" s="7" t="n"/>
-      <c r="Q37" s="6" t="n"/>
+      <c r="Q37" s="7" t="n"/>
       <c r="R37" s="6" t="n"/>
+      <c r="S37" s="6" t="n"/>
+      <c r="T37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
@@ -1379,8 +1467,10 @@
       <c r="N38" s="7" t="n"/>
       <c r="O38" s="7" t="n"/>
       <c r="P38" s="7" t="n"/>
-      <c r="Q38" s="6" t="n"/>
+      <c r="Q38" s="7" t="n"/>
       <c r="R38" s="6" t="n"/>
+      <c r="S38" s="6" t="n"/>
+      <c r="T38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
@@ -1399,8 +1489,10 @@
       <c r="N39" s="7" t="n"/>
       <c r="O39" s="7" t="n"/>
       <c r="P39" s="7" t="n"/>
-      <c r="Q39" s="6" t="n"/>
+      <c r="Q39" s="7" t="n"/>
       <c r="R39" s="6" t="n"/>
+      <c r="S39" s="6" t="n"/>
+      <c r="T39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -1419,8 +1511,10 @@
       <c r="N40" s="7" t="n"/>
       <c r="O40" s="7" t="n"/>
       <c r="P40" s="7" t="n"/>
-      <c r="Q40" s="6" t="n"/>
+      <c r="Q40" s="7" t="n"/>
       <c r="R40" s="6" t="n"/>
+      <c r="S40" s="6" t="n"/>
+      <c r="T40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
@@ -1439,8 +1533,10 @@
       <c r="N41" s="7" t="n"/>
       <c r="O41" s="7" t="n"/>
       <c r="P41" s="7" t="n"/>
-      <c r="Q41" s="6" t="n"/>
+      <c r="Q41" s="7" t="n"/>
       <c r="R41" s="6" t="n"/>
+      <c r="S41" s="6" t="n"/>
+      <c r="T41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
@@ -1459,8 +1555,10 @@
       <c r="N42" s="7" t="n"/>
       <c r="O42" s="7" t="n"/>
       <c r="P42" s="7" t="n"/>
-      <c r="Q42" s="6" t="n"/>
+      <c r="Q42" s="7" t="n"/>
       <c r="R42" s="6" t="n"/>
+      <c r="S42" s="6" t="n"/>
+      <c r="T42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
@@ -1479,8 +1577,10 @@
       <c r="N43" s="7" t="n"/>
       <c r="O43" s="7" t="n"/>
       <c r="P43" s="7" t="n"/>
-      <c r="Q43" s="6" t="n"/>
+      <c r="Q43" s="7" t="n"/>
       <c r="R43" s="6" t="n"/>
+      <c r="S43" s="6" t="n"/>
+      <c r="T43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -1499,8 +1599,10 @@
       <c r="N44" s="7" t="n"/>
       <c r="O44" s="7" t="n"/>
       <c r="P44" s="7" t="n"/>
-      <c r="Q44" s="6" t="n"/>
+      <c r="Q44" s="7" t="n"/>
       <c r="R44" s="6" t="n"/>
+      <c r="S44" s="6" t="n"/>
+      <c r="T44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
@@ -1519,8 +1621,10 @@
       <c r="N45" s="7" t="n"/>
       <c r="O45" s="7" t="n"/>
       <c r="P45" s="7" t="n"/>
-      <c r="Q45" s="6" t="n"/>
+      <c r="Q45" s="7" t="n"/>
       <c r="R45" s="6" t="n"/>
+      <c r="S45" s="6" t="n"/>
+      <c r="T45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n"/>
@@ -1539,8 +1643,10 @@
       <c r="N46" s="7" t="n"/>
       <c r="O46" s="7" t="n"/>
       <c r="P46" s="7" t="n"/>
-      <c r="Q46" s="6" t="n"/>
+      <c r="Q46" s="7" t="n"/>
       <c r="R46" s="6" t="n"/>
+      <c r="S46" s="6" t="n"/>
+      <c r="T46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>
@@ -1559,8 +1665,10 @@
       <c r="N47" s="7" t="n"/>
       <c r="O47" s="7" t="n"/>
       <c r="P47" s="7" t="n"/>
-      <c r="Q47" s="6" t="n"/>
+      <c r="Q47" s="7" t="n"/>
       <c r="R47" s="6" t="n"/>
+      <c r="S47" s="6" t="n"/>
+      <c r="T47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -1579,8 +1687,10 @@
       <c r="N48" s="7" t="n"/>
       <c r="O48" s="7" t="n"/>
       <c r="P48" s="7" t="n"/>
-      <c r="Q48" s="6" t="n"/>
+      <c r="Q48" s="7" t="n"/>
       <c r="R48" s="6" t="n"/>
+      <c r="S48" s="6" t="n"/>
+      <c r="T48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
@@ -1599,8 +1709,10 @@
       <c r="N49" s="7" t="n"/>
       <c r="O49" s="7" t="n"/>
       <c r="P49" s="7" t="n"/>
-      <c r="Q49" s="6" t="n"/>
+      <c r="Q49" s="7" t="n"/>
       <c r="R49" s="6" t="n"/>
+      <c r="S49" s="6" t="n"/>
+      <c r="T49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n"/>
@@ -1619,8 +1731,10 @@
       <c r="N50" s="7" t="n"/>
       <c r="O50" s="7" t="n"/>
       <c r="P50" s="7" t="n"/>
-      <c r="Q50" s="6" t="n"/>
+      <c r="Q50" s="7" t="n"/>
       <c r="R50" s="6" t="n"/>
+      <c r="S50" s="6" t="n"/>
+      <c r="T50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n"/>
@@ -1639,8 +1753,10 @@
       <c r="N51" s="7" t="n"/>
       <c r="O51" s="7" t="n"/>
       <c r="P51" s="7" t="n"/>
-      <c r="Q51" s="6" t="n"/>
+      <c r="Q51" s="7" t="n"/>
       <c r="R51" s="6" t="n"/>
+      <c r="S51" s="6" t="n"/>
+      <c r="T51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -1659,8 +1775,10 @@
       <c r="N52" s="7" t="n"/>
       <c r="O52" s="7" t="n"/>
       <c r="P52" s="7" t="n"/>
-      <c r="Q52" s="6" t="n"/>
+      <c r="Q52" s="7" t="n"/>
       <c r="R52" s="6" t="n"/>
+      <c r="S52" s="6" t="n"/>
+      <c r="T52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n"/>
@@ -1679,8 +1797,10 @@
       <c r="N53" s="7" t="n"/>
       <c r="O53" s="7" t="n"/>
       <c r="P53" s="7" t="n"/>
-      <c r="Q53" s="6" t="n"/>
+      <c r="Q53" s="7" t="n"/>
       <c r="R53" s="6" t="n"/>
+      <c r="S53" s="6" t="n"/>
+      <c r="T53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n"/>
@@ -1699,8 +1819,10 @@
       <c r="N54" s="7" t="n"/>
       <c r="O54" s="7" t="n"/>
       <c r="P54" s="7" t="n"/>
-      <c r="Q54" s="6" t="n"/>
+      <c r="Q54" s="7" t="n"/>
       <c r="R54" s="6" t="n"/>
+      <c r="S54" s="6" t="n"/>
+      <c r="T54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>
@@ -1719,8 +1841,10 @@
       <c r="N55" s="7" t="n"/>
       <c r="O55" s="7" t="n"/>
       <c r="P55" s="7" t="n"/>
-      <c r="Q55" s="6" t="n"/>
+      <c r="Q55" s="7" t="n"/>
       <c r="R55" s="6" t="n"/>
+      <c r="S55" s="6" t="n"/>
+      <c r="T55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -1739,8 +1863,10 @@
       <c r="N56" s="7" t="n"/>
       <c r="O56" s="7" t="n"/>
       <c r="P56" s="7" t="n"/>
-      <c r="Q56" s="6" t="n"/>
+      <c r="Q56" s="7" t="n"/>
       <c r="R56" s="6" t="n"/>
+      <c r="S56" s="6" t="n"/>
+      <c r="T56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n"/>
@@ -1759,8 +1885,10 @@
       <c r="N57" s="7" t="n"/>
       <c r="O57" s="7" t="n"/>
       <c r="P57" s="7" t="n"/>
-      <c r="Q57" s="6" t="n"/>
+      <c r="Q57" s="7" t="n"/>
       <c r="R57" s="6" t="n"/>
+      <c r="S57" s="6" t="n"/>
+      <c r="T57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n"/>
@@ -1779,8 +1907,10 @@
       <c r="N58" s="7" t="n"/>
       <c r="O58" s="7" t="n"/>
       <c r="P58" s="7" t="n"/>
-      <c r="Q58" s="6" t="n"/>
+      <c r="Q58" s="7" t="n"/>
       <c r="R58" s="6" t="n"/>
+      <c r="S58" s="6" t="n"/>
+      <c r="T58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n"/>
@@ -1799,8 +1929,10 @@
       <c r="N59" s="7" t="n"/>
       <c r="O59" s="7" t="n"/>
       <c r="P59" s="7" t="n"/>
-      <c r="Q59" s="6" t="n"/>
+      <c r="Q59" s="7" t="n"/>
       <c r="R59" s="6" t="n"/>
+      <c r="S59" s="6" t="n"/>
+      <c r="T59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -1819,8 +1951,10 @@
       <c r="N60" s="7" t="n"/>
       <c r="O60" s="7" t="n"/>
       <c r="P60" s="7" t="n"/>
-      <c r="Q60" s="6" t="n"/>
+      <c r="Q60" s="7" t="n"/>
       <c r="R60" s="6" t="n"/>
+      <c r="S60" s="6" t="n"/>
+      <c r="T60" s="6" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n"/>
@@ -1839,8 +1973,10 @@
       <c r="N61" s="7" t="n"/>
       <c r="O61" s="7" t="n"/>
       <c r="P61" s="7" t="n"/>
-      <c r="Q61" s="6" t="n"/>
+      <c r="Q61" s="7" t="n"/>
       <c r="R61" s="6" t="n"/>
+      <c r="S61" s="6" t="n"/>
+      <c r="T61" s="6" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n"/>
@@ -1859,8 +1995,10 @@
       <c r="N62" s="7" t="n"/>
       <c r="O62" s="7" t="n"/>
       <c r="P62" s="7" t="n"/>
-      <c r="Q62" s="6" t="n"/>
+      <c r="Q62" s="7" t="n"/>
       <c r="R62" s="6" t="n"/>
+      <c r="S62" s="6" t="n"/>
+      <c r="T62" s="6" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n"/>
@@ -1879,8 +2017,10 @@
       <c r="N63" s="7" t="n"/>
       <c r="O63" s="7" t="n"/>
       <c r="P63" s="7" t="n"/>
-      <c r="Q63" s="6" t="n"/>
+      <c r="Q63" s="7" t="n"/>
       <c r="R63" s="6" t="n"/>
+      <c r="S63" s="6" t="n"/>
+      <c r="T63" s="6" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
@@ -1899,8 +2039,10 @@
       <c r="N64" s="7" t="n"/>
       <c r="O64" s="7" t="n"/>
       <c r="P64" s="7" t="n"/>
-      <c r="Q64" s="6" t="n"/>
+      <c r="Q64" s="7" t="n"/>
       <c r="R64" s="6" t="n"/>
+      <c r="S64" s="6" t="n"/>
+      <c r="T64" s="6" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n"/>
@@ -1919,8 +2061,10 @@
       <c r="N65" s="7" t="n"/>
       <c r="O65" s="7" t="n"/>
       <c r="P65" s="7" t="n"/>
-      <c r="Q65" s="6" t="n"/>
+      <c r="Q65" s="7" t="n"/>
       <c r="R65" s="6" t="n"/>
+      <c r="S65" s="6" t="n"/>
+      <c r="T65" s="6" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n"/>
@@ -1939,8 +2083,10 @@
       <c r="N66" s="7" t="n"/>
       <c r="O66" s="7" t="n"/>
       <c r="P66" s="7" t="n"/>
-      <c r="Q66" s="6" t="n"/>
+      <c r="Q66" s="7" t="n"/>
       <c r="R66" s="6" t="n"/>
+      <c r="S66" s="6" t="n"/>
+      <c r="T66" s="6" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n"/>
@@ -1959,8 +2105,10 @@
       <c r="N67" s="7" t="n"/>
       <c r="O67" s="7" t="n"/>
       <c r="P67" s="7" t="n"/>
-      <c r="Q67" s="6" t="n"/>
+      <c r="Q67" s="7" t="n"/>
       <c r="R67" s="6" t="n"/>
+      <c r="S67" s="6" t="n"/>
+      <c r="T67" s="6" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -1979,8 +2127,10 @@
       <c r="N68" s="7" t="n"/>
       <c r="O68" s="7" t="n"/>
       <c r="P68" s="7" t="n"/>
-      <c r="Q68" s="6" t="n"/>
+      <c r="Q68" s="7" t="n"/>
       <c r="R68" s="6" t="n"/>
+      <c r="S68" s="6" t="n"/>
+      <c r="T68" s="6" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n"/>
@@ -1999,8 +2149,10 @@
       <c r="N69" s="7" t="n"/>
       <c r="O69" s="7" t="n"/>
       <c r="P69" s="7" t="n"/>
-      <c r="Q69" s="6" t="n"/>
+      <c r="Q69" s="7" t="n"/>
       <c r="R69" s="6" t="n"/>
+      <c r="S69" s="6" t="n"/>
+      <c r="T69" s="6" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n"/>
@@ -2019,8 +2171,10 @@
       <c r="N70" s="7" t="n"/>
       <c r="O70" s="7" t="n"/>
       <c r="P70" s="7" t="n"/>
-      <c r="Q70" s="6" t="n"/>
+      <c r="Q70" s="7" t="n"/>
       <c r="R70" s="6" t="n"/>
+      <c r="S70" s="6" t="n"/>
+      <c r="T70" s="6" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n"/>
@@ -2039,8 +2193,10 @@
       <c r="N71" s="7" t="n"/>
       <c r="O71" s="7" t="n"/>
       <c r="P71" s="7" t="n"/>
-      <c r="Q71" s="6" t="n"/>
+      <c r="Q71" s="7" t="n"/>
       <c r="R71" s="6" t="n"/>
+      <c r="S71" s="6" t="n"/>
+      <c r="T71" s="6" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n"/>
@@ -2059,8 +2215,10 @@
       <c r="N72" s="7" t="n"/>
       <c r="O72" s="7" t="n"/>
       <c r="P72" s="7" t="n"/>
-      <c r="Q72" s="6" t="n"/>
+      <c r="Q72" s="7" t="n"/>
       <c r="R72" s="6" t="n"/>
+      <c r="S72" s="6" t="n"/>
+      <c r="T72" s="6" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n"/>
@@ -2079,8 +2237,10 @@
       <c r="N73" s="7" t="n"/>
       <c r="O73" s="7" t="n"/>
       <c r="P73" s="7" t="n"/>
-      <c r="Q73" s="6" t="n"/>
+      <c r="Q73" s="7" t="n"/>
       <c r="R73" s="6" t="n"/>
+      <c r="S73" s="6" t="n"/>
+      <c r="T73" s="6" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n"/>
@@ -2099,8 +2259,10 @@
       <c r="N74" s="7" t="n"/>
       <c r="O74" s="7" t="n"/>
       <c r="P74" s="7" t="n"/>
-      <c r="Q74" s="6" t="n"/>
+      <c r="Q74" s="7" t="n"/>
       <c r="R74" s="6" t="n"/>
+      <c r="S74" s="6" t="n"/>
+      <c r="T74" s="6" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n"/>
@@ -2119,8 +2281,10 @@
       <c r="N75" s="7" t="n"/>
       <c r="O75" s="7" t="n"/>
       <c r="P75" s="7" t="n"/>
-      <c r="Q75" s="6" t="n"/>
+      <c r="Q75" s="7" t="n"/>
       <c r="R75" s="6" t="n"/>
+      <c r="S75" s="6" t="n"/>
+      <c r="T75" s="6" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
@@ -2139,8 +2303,10 @@
       <c r="N76" s="7" t="n"/>
       <c r="O76" s="7" t="n"/>
       <c r="P76" s="7" t="n"/>
-      <c r="Q76" s="6" t="n"/>
+      <c r="Q76" s="7" t="n"/>
       <c r="R76" s="6" t="n"/>
+      <c r="S76" s="6" t="n"/>
+      <c r="T76" s="6" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="n"/>
@@ -2159,8 +2325,10 @@
       <c r="N77" s="7" t="n"/>
       <c r="O77" s="7" t="n"/>
       <c r="P77" s="7" t="n"/>
-      <c r="Q77" s="6" t="n"/>
+      <c r="Q77" s="7" t="n"/>
       <c r="R77" s="6" t="n"/>
+      <c r="S77" s="6" t="n"/>
+      <c r="T77" s="6" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="n"/>
@@ -2179,8 +2347,10 @@
       <c r="N78" s="7" t="n"/>
       <c r="O78" s="7" t="n"/>
       <c r="P78" s="7" t="n"/>
-      <c r="Q78" s="6" t="n"/>
+      <c r="Q78" s="7" t="n"/>
       <c r="R78" s="6" t="n"/>
+      <c r="S78" s="6" t="n"/>
+      <c r="T78" s="6" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="n"/>
@@ -2199,8 +2369,10 @@
       <c r="N79" s="7" t="n"/>
       <c r="O79" s="7" t="n"/>
       <c r="P79" s="7" t="n"/>
-      <c r="Q79" s="6" t="n"/>
+      <c r="Q79" s="7" t="n"/>
       <c r="R79" s="6" t="n"/>
+      <c r="S79" s="6" t="n"/>
+      <c r="T79" s="6" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
@@ -2219,8 +2391,10 @@
       <c r="N80" s="7" t="n"/>
       <c r="O80" s="7" t="n"/>
       <c r="P80" s="7" t="n"/>
-      <c r="Q80" s="6" t="n"/>
+      <c r="Q80" s="7" t="n"/>
       <c r="R80" s="6" t="n"/>
+      <c r="S80" s="6" t="n"/>
+      <c r="T80" s="6" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="n"/>
@@ -2239,8 +2413,10 @@
       <c r="N81" s="7" t="n"/>
       <c r="O81" s="7" t="n"/>
       <c r="P81" s="7" t="n"/>
-      <c r="Q81" s="6" t="n"/>
+      <c r="Q81" s="7" t="n"/>
       <c r="R81" s="6" t="n"/>
+      <c r="S81" s="6" t="n"/>
+      <c r="T81" s="6" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n"/>
@@ -2259,8 +2435,10 @@
       <c r="N82" s="7" t="n"/>
       <c r="O82" s="7" t="n"/>
       <c r="P82" s="7" t="n"/>
-      <c r="Q82" s="6" t="n"/>
+      <c r="Q82" s="7" t="n"/>
       <c r="R82" s="6" t="n"/>
+      <c r="S82" s="6" t="n"/>
+      <c r="T82" s="6" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n"/>
@@ -2279,8 +2457,10 @@
       <c r="N83" s="7" t="n"/>
       <c r="O83" s="7" t="n"/>
       <c r="P83" s="7" t="n"/>
-      <c r="Q83" s="6" t="n"/>
+      <c r="Q83" s="7" t="n"/>
       <c r="R83" s="6" t="n"/>
+      <c r="S83" s="6" t="n"/>
+      <c r="T83" s="6" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n"/>
@@ -2299,8 +2479,10 @@
       <c r="N84" s="7" t="n"/>
       <c r="O84" s="7" t="n"/>
       <c r="P84" s="7" t="n"/>
-      <c r="Q84" s="6" t="n"/>
+      <c r="Q84" s="7" t="n"/>
       <c r="R84" s="6" t="n"/>
+      <c r="S84" s="6" t="n"/>
+      <c r="T84" s="6" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="n"/>
@@ -2319,8 +2501,10 @@
       <c r="N85" s="7" t="n"/>
       <c r="O85" s="7" t="n"/>
       <c r="P85" s="7" t="n"/>
-      <c r="Q85" s="6" t="n"/>
+      <c r="Q85" s="7" t="n"/>
       <c r="R85" s="6" t="n"/>
+      <c r="S85" s="6" t="n"/>
+      <c r="T85" s="6" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="n"/>
@@ -2339,8 +2523,10 @@
       <c r="N86" s="7" t="n"/>
       <c r="O86" s="7" t="n"/>
       <c r="P86" s="7" t="n"/>
-      <c r="Q86" s="6" t="n"/>
+      <c r="Q86" s="7" t="n"/>
       <c r="R86" s="6" t="n"/>
+      <c r="S86" s="6" t="n"/>
+      <c r="T86" s="6" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="6" t="n"/>
@@ -2359,8 +2545,10 @@
       <c r="N87" s="7" t="n"/>
       <c r="O87" s="7" t="n"/>
       <c r="P87" s="7" t="n"/>
-      <c r="Q87" s="6" t="n"/>
+      <c r="Q87" s="7" t="n"/>
       <c r="R87" s="6" t="n"/>
+      <c r="S87" s="6" t="n"/>
+      <c r="T87" s="6" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="n"/>
@@ -2379,8 +2567,10 @@
       <c r="N88" s="7" t="n"/>
       <c r="O88" s="7" t="n"/>
       <c r="P88" s="7" t="n"/>
-      <c r="Q88" s="6" t="n"/>
+      <c r="Q88" s="7" t="n"/>
       <c r="R88" s="6" t="n"/>
+      <c r="S88" s="6" t="n"/>
+      <c r="T88" s="6" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="6" t="n"/>
@@ -2399,8 +2589,10 @@
       <c r="N89" s="7" t="n"/>
       <c r="O89" s="7" t="n"/>
       <c r="P89" s="7" t="n"/>
-      <c r="Q89" s="6" t="n"/>
+      <c r="Q89" s="7" t="n"/>
       <c r="R89" s="6" t="n"/>
+      <c r="S89" s="6" t="n"/>
+      <c r="T89" s="6" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n"/>
@@ -2419,8 +2611,10 @@
       <c r="N90" s="7" t="n"/>
       <c r="O90" s="7" t="n"/>
       <c r="P90" s="7" t="n"/>
-      <c r="Q90" s="6" t="n"/>
+      <c r="Q90" s="7" t="n"/>
       <c r="R90" s="6" t="n"/>
+      <c r="S90" s="6" t="n"/>
+      <c r="T90" s="6" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n"/>
@@ -2439,8 +2633,10 @@
       <c r="N91" s="7" t="n"/>
       <c r="O91" s="7" t="n"/>
       <c r="P91" s="7" t="n"/>
-      <c r="Q91" s="6" t="n"/>
+      <c r="Q91" s="7" t="n"/>
       <c r="R91" s="6" t="n"/>
+      <c r="S91" s="6" t="n"/>
+      <c r="T91" s="6" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n"/>
@@ -2459,8 +2655,10 @@
       <c r="N92" s="7" t="n"/>
       <c r="O92" s="7" t="n"/>
       <c r="P92" s="7" t="n"/>
-      <c r="Q92" s="6" t="n"/>
+      <c r="Q92" s="7" t="n"/>
       <c r="R92" s="6" t="n"/>
+      <c r="S92" s="6" t="n"/>
+      <c r="T92" s="6" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n"/>
@@ -2479,8 +2677,10 @@
       <c r="N93" s="7" t="n"/>
       <c r="O93" s="7" t="n"/>
       <c r="P93" s="7" t="n"/>
-      <c r="Q93" s="6" t="n"/>
+      <c r="Q93" s="7" t="n"/>
       <c r="R93" s="6" t="n"/>
+      <c r="S93" s="6" t="n"/>
+      <c r="T93" s="6" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n"/>
@@ -2499,8 +2699,10 @@
       <c r="N94" s="7" t="n"/>
       <c r="O94" s="7" t="n"/>
       <c r="P94" s="7" t="n"/>
-      <c r="Q94" s="6" t="n"/>
+      <c r="Q94" s="7" t="n"/>
       <c r="R94" s="6" t="n"/>
+      <c r="S94" s="6" t="n"/>
+      <c r="T94" s="6" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n"/>
@@ -2519,8 +2721,10 @@
       <c r="N95" s="7" t="n"/>
       <c r="O95" s="7" t="n"/>
       <c r="P95" s="7" t="n"/>
-      <c r="Q95" s="6" t="n"/>
+      <c r="Q95" s="7" t="n"/>
       <c r="R95" s="6" t="n"/>
+      <c r="S95" s="6" t="n"/>
+      <c r="T95" s="6" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n"/>
@@ -2539,8 +2743,10 @@
       <c r="N96" s="7" t="n"/>
       <c r="O96" s="7" t="n"/>
       <c r="P96" s="7" t="n"/>
-      <c r="Q96" s="6" t="n"/>
+      <c r="Q96" s="7" t="n"/>
       <c r="R96" s="6" t="n"/>
+      <c r="S96" s="6" t="n"/>
+      <c r="T96" s="6" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n"/>
@@ -2559,8 +2765,10 @@
       <c r="N97" s="7" t="n"/>
       <c r="O97" s="7" t="n"/>
       <c r="P97" s="7" t="n"/>
-      <c r="Q97" s="6" t="n"/>
+      <c r="Q97" s="7" t="n"/>
       <c r="R97" s="6" t="n"/>
+      <c r="S97" s="6" t="n"/>
+      <c r="T97" s="6" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n"/>
@@ -2579,8 +2787,10 @@
       <c r="N98" s="7" t="n"/>
       <c r="O98" s="7" t="n"/>
       <c r="P98" s="7" t="n"/>
-      <c r="Q98" s="6" t="n"/>
+      <c r="Q98" s="7" t="n"/>
       <c r="R98" s="6" t="n"/>
+      <c r="S98" s="6" t="n"/>
+      <c r="T98" s="6" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n"/>
@@ -2599,8 +2809,10 @@
       <c r="N99" s="7" t="n"/>
       <c r="O99" s="7" t="n"/>
       <c r="P99" s="7" t="n"/>
-      <c r="Q99" s="6" t="n"/>
+      <c r="Q99" s="7" t="n"/>
       <c r="R99" s="6" t="n"/>
+      <c r="S99" s="6" t="n"/>
+      <c r="T99" s="6" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n"/>
@@ -2619,8 +2831,10 @@
       <c r="N100" s="7" t="n"/>
       <c r="O100" s="7" t="n"/>
       <c r="P100" s="7" t="n"/>
-      <c r="Q100" s="6" t="n"/>
+      <c r="Q100" s="7" t="n"/>
       <c r="R100" s="6" t="n"/>
+      <c r="S100" s="6" t="n"/>
+      <c r="T100" s="6" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n"/>
@@ -2639,8 +2853,10 @@
       <c r="N101" s="7" t="n"/>
       <c r="O101" s="7" t="n"/>
       <c r="P101" s="7" t="n"/>
-      <c r="Q101" s="6" t="n"/>
+      <c r="Q101" s="7" t="n"/>
       <c r="R101" s="6" t="n"/>
+      <c r="S101" s="6" t="n"/>
+      <c r="T101" s="6" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="n"/>
@@ -2659,8 +2875,10 @@
       <c r="N102" s="7" t="n"/>
       <c r="O102" s="7" t="n"/>
       <c r="P102" s="7" t="n"/>
-      <c r="Q102" s="6" t="n"/>
+      <c r="Q102" s="7" t="n"/>
       <c r="R102" s="6" t="n"/>
+      <c r="S102" s="6" t="n"/>
+      <c r="T102" s="6" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="6" t="n"/>
@@ -2679,8 +2897,10 @@
       <c r="N103" s="7" t="n"/>
       <c r="O103" s="7" t="n"/>
       <c r="P103" s="7" t="n"/>
-      <c r="Q103" s="6" t="n"/>
+      <c r="Q103" s="7" t="n"/>
       <c r="R103" s="6" t="n"/>
+      <c r="S103" s="6" t="n"/>
+      <c r="T103" s="6" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="n"/>
@@ -2699,8 +2919,10 @@
       <c r="N104" s="7" t="n"/>
       <c r="O104" s="7" t="n"/>
       <c r="P104" s="7" t="n"/>
-      <c r="Q104" s="6" t="n"/>
+      <c r="Q104" s="7" t="n"/>
       <c r="R104" s="6" t="n"/>
+      <c r="S104" s="6" t="n"/>
+      <c r="T104" s="6" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="6" t="n"/>
@@ -2719,8 +2941,10 @@
       <c r="N105" s="7" t="n"/>
       <c r="O105" s="7" t="n"/>
       <c r="P105" s="7" t="n"/>
-      <c r="Q105" s="6" t="n"/>
+      <c r="Q105" s="7" t="n"/>
       <c r="R105" s="6" t="n"/>
+      <c r="S105" s="6" t="n"/>
+      <c r="T105" s="6" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="n"/>
@@ -2739,8 +2963,10 @@
       <c r="N106" s="7" t="n"/>
       <c r="O106" s="7" t="n"/>
       <c r="P106" s="7" t="n"/>
-      <c r="Q106" s="6" t="n"/>
+      <c r="Q106" s="7" t="n"/>
       <c r="R106" s="6" t="n"/>
+      <c r="S106" s="6" t="n"/>
+      <c r="T106" s="6" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="6" t="n"/>
@@ -2759,8 +2985,10 @@
       <c r="N107" s="7" t="n"/>
       <c r="O107" s="7" t="n"/>
       <c r="P107" s="7" t="n"/>
-      <c r="Q107" s="6" t="n"/>
+      <c r="Q107" s="7" t="n"/>
       <c r="R107" s="6" t="n"/>
+      <c r="S107" s="6" t="n"/>
+      <c r="T107" s="6" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="n"/>
@@ -2779,8 +3007,10 @@
       <c r="N108" s="7" t="n"/>
       <c r="O108" s="7" t="n"/>
       <c r="P108" s="7" t="n"/>
-      <c r="Q108" s="6" t="n"/>
+      <c r="Q108" s="7" t="n"/>
       <c r="R108" s="6" t="n"/>
+      <c r="S108" s="6" t="n"/>
+      <c r="T108" s="6" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="6" t="n"/>
@@ -2799,8 +3029,10 @@
       <c r="N109" s="7" t="n"/>
       <c r="O109" s="7" t="n"/>
       <c r="P109" s="7" t="n"/>
-      <c r="Q109" s="6" t="n"/>
+      <c r="Q109" s="7" t="n"/>
       <c r="R109" s="6" t="n"/>
+      <c r="S109" s="6" t="n"/>
+      <c r="T109" s="6" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="n"/>
@@ -2819,8 +3051,10 @@
       <c r="N110" s="7" t="n"/>
       <c r="O110" s="7" t="n"/>
       <c r="P110" s="7" t="n"/>
-      <c r="Q110" s="6" t="n"/>
+      <c r="Q110" s="7" t="n"/>
       <c r="R110" s="6" t="n"/>
+      <c r="S110" s="6" t="n"/>
+      <c r="T110" s="6" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="6" t="n"/>
@@ -2839,8 +3073,10 @@
       <c r="N111" s="7" t="n"/>
       <c r="O111" s="7" t="n"/>
       <c r="P111" s="7" t="n"/>
-      <c r="Q111" s="6" t="n"/>
+      <c r="Q111" s="7" t="n"/>
       <c r="R111" s="6" t="n"/>
+      <c r="S111" s="6" t="n"/>
+      <c r="T111" s="6" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="n"/>
@@ -2859,8 +3095,10 @@
       <c r="N112" s="7" t="n"/>
       <c r="O112" s="7" t="n"/>
       <c r="P112" s="7" t="n"/>
-      <c r="Q112" s="6" t="n"/>
+      <c r="Q112" s="7" t="n"/>
       <c r="R112" s="6" t="n"/>
+      <c r="S112" s="6" t="n"/>
+      <c r="T112" s="6" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="6" t="n"/>
@@ -2879,8 +3117,10 @@
       <c r="N113" s="7" t="n"/>
       <c r="O113" s="7" t="n"/>
       <c r="P113" s="7" t="n"/>
-      <c r="Q113" s="6" t="n"/>
+      <c r="Q113" s="7" t="n"/>
       <c r="R113" s="6" t="n"/>
+      <c r="S113" s="6" t="n"/>
+      <c r="T113" s="6" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="n"/>
@@ -2899,8 +3139,10 @@
       <c r="N114" s="7" t="n"/>
       <c r="O114" s="7" t="n"/>
       <c r="P114" s="7" t="n"/>
-      <c r="Q114" s="6" t="n"/>
+      <c r="Q114" s="7" t="n"/>
       <c r="R114" s="6" t="n"/>
+      <c r="S114" s="6" t="n"/>
+      <c r="T114" s="6" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="6" t="n"/>
@@ -2919,8 +3161,10 @@
       <c r="N115" s="7" t="n"/>
       <c r="O115" s="7" t="n"/>
       <c r="P115" s="7" t="n"/>
-      <c r="Q115" s="6" t="n"/>
+      <c r="Q115" s="7" t="n"/>
       <c r="R115" s="6" t="n"/>
+      <c r="S115" s="6" t="n"/>
+      <c r="T115" s="6" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="n"/>
@@ -2939,8 +3183,10 @@
       <c r="N116" s="7" t="n"/>
       <c r="O116" s="7" t="n"/>
       <c r="P116" s="7" t="n"/>
-      <c r="Q116" s="6" t="n"/>
+      <c r="Q116" s="7" t="n"/>
       <c r="R116" s="6" t="n"/>
+      <c r="S116" s="6" t="n"/>
+      <c r="T116" s="6" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="6" t="n"/>
@@ -2959,8 +3205,10 @@
       <c r="N117" s="7" t="n"/>
       <c r="O117" s="7" t="n"/>
       <c r="P117" s="7" t="n"/>
-      <c r="Q117" s="6" t="n"/>
+      <c r="Q117" s="7" t="n"/>
       <c r="R117" s="6" t="n"/>
+      <c r="S117" s="6" t="n"/>
+      <c r="T117" s="6" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="n"/>
@@ -2979,8 +3227,10 @@
       <c r="N118" s="7" t="n"/>
       <c r="O118" s="7" t="n"/>
       <c r="P118" s="7" t="n"/>
-      <c r="Q118" s="6" t="n"/>
+      <c r="Q118" s="7" t="n"/>
       <c r="R118" s="6" t="n"/>
+      <c r="S118" s="6" t="n"/>
+      <c r="T118" s="6" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="6" t="n"/>
@@ -2999,8 +3249,10 @@
       <c r="N119" s="7" t="n"/>
       <c r="O119" s="7" t="n"/>
       <c r="P119" s="7" t="n"/>
-      <c r="Q119" s="6" t="n"/>
+      <c r="Q119" s="7" t="n"/>
       <c r="R119" s="6" t="n"/>
+      <c r="S119" s="6" t="n"/>
+      <c r="T119" s="6" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="n"/>
@@ -3019,8 +3271,10 @@
       <c r="N120" s="7" t="n"/>
       <c r="O120" s="7" t="n"/>
       <c r="P120" s="7" t="n"/>
-      <c r="Q120" s="6" t="n"/>
+      <c r="Q120" s="7" t="n"/>
       <c r="R120" s="6" t="n"/>
+      <c r="S120" s="6" t="n"/>
+      <c r="T120" s="6" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="6" t="n"/>
@@ -3039,8 +3293,10 @@
       <c r="N121" s="7" t="n"/>
       <c r="O121" s="7" t="n"/>
       <c r="P121" s="7" t="n"/>
-      <c r="Q121" s="6" t="n"/>
+      <c r="Q121" s="7" t="n"/>
       <c r="R121" s="6" t="n"/>
+      <c r="S121" s="6" t="n"/>
+      <c r="T121" s="6" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="6" t="n"/>
@@ -3059,8 +3315,10 @@
       <c r="N122" s="7" t="n"/>
       <c r="O122" s="7" t="n"/>
       <c r="P122" s="7" t="n"/>
-      <c r="Q122" s="6" t="n"/>
+      <c r="Q122" s="7" t="n"/>
       <c r="R122" s="6" t="n"/>
+      <c r="S122" s="6" t="n"/>
+      <c r="T122" s="6" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="6" t="n"/>
@@ -3079,8 +3337,10 @@
       <c r="N123" s="7" t="n"/>
       <c r="O123" s="7" t="n"/>
       <c r="P123" s="7" t="n"/>
-      <c r="Q123" s="6" t="n"/>
+      <c r="Q123" s="7" t="n"/>
       <c r="R123" s="6" t="n"/>
+      <c r="S123" s="6" t="n"/>
+      <c r="T123" s="6" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="6" t="n"/>
@@ -3099,8 +3359,10 @@
       <c r="N124" s="7" t="n"/>
       <c r="O124" s="7" t="n"/>
       <c r="P124" s="7" t="n"/>
-      <c r="Q124" s="6" t="n"/>
+      <c r="Q124" s="7" t="n"/>
       <c r="R124" s="6" t="n"/>
+      <c r="S124" s="6" t="n"/>
+      <c r="T124" s="6" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="6" t="n"/>
@@ -3119,8 +3381,10 @@
       <c r="N125" s="7" t="n"/>
       <c r="O125" s="7" t="n"/>
       <c r="P125" s="7" t="n"/>
-      <c r="Q125" s="6" t="n"/>
+      <c r="Q125" s="7" t="n"/>
       <c r="R125" s="6" t="n"/>
+      <c r="S125" s="6" t="n"/>
+      <c r="T125" s="6" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="6" t="n"/>
@@ -3139,8 +3403,10 @@
       <c r="N126" s="7" t="n"/>
       <c r="O126" s="7" t="n"/>
       <c r="P126" s="7" t="n"/>
-      <c r="Q126" s="6" t="n"/>
+      <c r="Q126" s="7" t="n"/>
       <c r="R126" s="6" t="n"/>
+      <c r="S126" s="6" t="n"/>
+      <c r="T126" s="6" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="6" t="n"/>
@@ -3159,8 +3425,10 @@
       <c r="N127" s="7" t="n"/>
       <c r="O127" s="7" t="n"/>
       <c r="P127" s="7" t="n"/>
-      <c r="Q127" s="6" t="n"/>
+      <c r="Q127" s="7" t="n"/>
       <c r="R127" s="6" t="n"/>
+      <c r="S127" s="6" t="n"/>
+      <c r="T127" s="6" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="6" t="n"/>
@@ -3179,8 +3447,10 @@
       <c r="N128" s="7" t="n"/>
       <c r="O128" s="7" t="n"/>
       <c r="P128" s="7" t="n"/>
-      <c r="Q128" s="6" t="n"/>
+      <c r="Q128" s="7" t="n"/>
       <c r="R128" s="6" t="n"/>
+      <c r="S128" s="6" t="n"/>
+      <c r="T128" s="6" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="6" t="n"/>
@@ -3199,8 +3469,10 @@
       <c r="N129" s="7" t="n"/>
       <c r="O129" s="7" t="n"/>
       <c r="P129" s="7" t="n"/>
-      <c r="Q129" s="6" t="n"/>
+      <c r="Q129" s="7" t="n"/>
       <c r="R129" s="6" t="n"/>
+      <c r="S129" s="6" t="n"/>
+      <c r="T129" s="6" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="6" t="n"/>
@@ -3219,8 +3491,10 @@
       <c r="N130" s="7" t="n"/>
       <c r="O130" s="7" t="n"/>
       <c r="P130" s="7" t="n"/>
-      <c r="Q130" s="6" t="n"/>
+      <c r="Q130" s="7" t="n"/>
       <c r="R130" s="6" t="n"/>
+      <c r="S130" s="6" t="n"/>
+      <c r="T130" s="6" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="6" t="n"/>
@@ -3239,8 +3513,10 @@
       <c r="N131" s="7" t="n"/>
       <c r="O131" s="7" t="n"/>
       <c r="P131" s="7" t="n"/>
-      <c r="Q131" s="6" t="n"/>
+      <c r="Q131" s="7" t="n"/>
       <c r="R131" s="6" t="n"/>
+      <c r="S131" s="6" t="n"/>
+      <c r="T131" s="6" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="6" t="n"/>
@@ -3259,8 +3535,10 @@
       <c r="N132" s="7" t="n"/>
       <c r="O132" s="7" t="n"/>
       <c r="P132" s="7" t="n"/>
-      <c r="Q132" s="6" t="n"/>
+      <c r="Q132" s="7" t="n"/>
       <c r="R132" s="6" t="n"/>
+      <c r="S132" s="6" t="n"/>
+      <c r="T132" s="6" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="6" t="n"/>
@@ -3279,8 +3557,10 @@
       <c r="N133" s="7" t="n"/>
       <c r="O133" s="7" t="n"/>
       <c r="P133" s="7" t="n"/>
-      <c r="Q133" s="6" t="n"/>
+      <c r="Q133" s="7" t="n"/>
       <c r="R133" s="6" t="n"/>
+      <c r="S133" s="6" t="n"/>
+      <c r="T133" s="6" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="n"/>
@@ -3299,8 +3579,10 @@
       <c r="N134" s="7" t="n"/>
       <c r="O134" s="7" t="n"/>
       <c r="P134" s="7" t="n"/>
-      <c r="Q134" s="6" t="n"/>
+      <c r="Q134" s="7" t="n"/>
       <c r="R134" s="6" t="n"/>
+      <c r="S134" s="6" t="n"/>
+      <c r="T134" s="6" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="6" t="n"/>
@@ -3319,8 +3601,10 @@
       <c r="N135" s="7" t="n"/>
       <c r="O135" s="7" t="n"/>
       <c r="P135" s="7" t="n"/>
-      <c r="Q135" s="6" t="n"/>
+      <c r="Q135" s="7" t="n"/>
       <c r="R135" s="6" t="n"/>
+      <c r="S135" s="6" t="n"/>
+      <c r="T135" s="6" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="n"/>
@@ -3339,8 +3623,10 @@
       <c r="N136" s="7" t="n"/>
       <c r="O136" s="7" t="n"/>
       <c r="P136" s="7" t="n"/>
-      <c r="Q136" s="6" t="n"/>
+      <c r="Q136" s="7" t="n"/>
       <c r="R136" s="6" t="n"/>
+      <c r="S136" s="6" t="n"/>
+      <c r="T136" s="6" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="6" t="n"/>
@@ -3359,8 +3645,10 @@
       <c r="N137" s="7" t="n"/>
       <c r="O137" s="7" t="n"/>
       <c r="P137" s="7" t="n"/>
-      <c r="Q137" s="6" t="n"/>
+      <c r="Q137" s="7" t="n"/>
       <c r="R137" s="6" t="n"/>
+      <c r="S137" s="6" t="n"/>
+      <c r="T137" s="6" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="n"/>
@@ -3379,8 +3667,10 @@
       <c r="N138" s="7" t="n"/>
       <c r="O138" s="7" t="n"/>
       <c r="P138" s="7" t="n"/>
-      <c r="Q138" s="6" t="n"/>
+      <c r="Q138" s="7" t="n"/>
       <c r="R138" s="6" t="n"/>
+      <c r="S138" s="6" t="n"/>
+      <c r="T138" s="6" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="6" t="n"/>
@@ -3399,8 +3689,10 @@
       <c r="N139" s="7" t="n"/>
       <c r="O139" s="7" t="n"/>
       <c r="P139" s="7" t="n"/>
-      <c r="Q139" s="6" t="n"/>
+      <c r="Q139" s="7" t="n"/>
       <c r="R139" s="6" t="n"/>
+      <c r="S139" s="6" t="n"/>
+      <c r="T139" s="6" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="6" t="n"/>
@@ -3419,8 +3711,10 @@
       <c r="N140" s="7" t="n"/>
       <c r="O140" s="7" t="n"/>
       <c r="P140" s="7" t="n"/>
-      <c r="Q140" s="6" t="n"/>
+      <c r="Q140" s="7" t="n"/>
       <c r="R140" s="6" t="n"/>
+      <c r="S140" s="6" t="n"/>
+      <c r="T140" s="6" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="6" t="n"/>
@@ -3439,8 +3733,10 @@
       <c r="N141" s="7" t="n"/>
       <c r="O141" s="7" t="n"/>
       <c r="P141" s="7" t="n"/>
-      <c r="Q141" s="6" t="n"/>
+      <c r="Q141" s="7" t="n"/>
       <c r="R141" s="6" t="n"/>
+      <c r="S141" s="6" t="n"/>
+      <c r="T141" s="6" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="6" t="n"/>
@@ -3459,8 +3755,10 @@
       <c r="N142" s="7" t="n"/>
       <c r="O142" s="7" t="n"/>
       <c r="P142" s="7" t="n"/>
-      <c r="Q142" s="6" t="n"/>
+      <c r="Q142" s="7" t="n"/>
       <c r="R142" s="6" t="n"/>
+      <c r="S142" s="6" t="n"/>
+      <c r="T142" s="6" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="6" t="n"/>
@@ -3479,8 +3777,10 @@
       <c r="N143" s="7" t="n"/>
       <c r="O143" s="7" t="n"/>
       <c r="P143" s="7" t="n"/>
-      <c r="Q143" s="6" t="n"/>
+      <c r="Q143" s="7" t="n"/>
       <c r="R143" s="6" t="n"/>
+      <c r="S143" s="6" t="n"/>
+      <c r="T143" s="6" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="6" t="n"/>
@@ -3499,8 +3799,10 @@
       <c r="N144" s="7" t="n"/>
       <c r="O144" s="7" t="n"/>
       <c r="P144" s="7" t="n"/>
-      <c r="Q144" s="6" t="n"/>
+      <c r="Q144" s="7" t="n"/>
       <c r="R144" s="6" t="n"/>
+      <c r="S144" s="6" t="n"/>
+      <c r="T144" s="6" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="6" t="n"/>
@@ -3519,8 +3821,10 @@
       <c r="N145" s="7" t="n"/>
       <c r="O145" s="7" t="n"/>
       <c r="P145" s="7" t="n"/>
-      <c r="Q145" s="6" t="n"/>
+      <c r="Q145" s="7" t="n"/>
       <c r="R145" s="6" t="n"/>
+      <c r="S145" s="6" t="n"/>
+      <c r="T145" s="6" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="6" t="n"/>
@@ -3539,8 +3843,10 @@
       <c r="N146" s="7" t="n"/>
       <c r="O146" s="7" t="n"/>
       <c r="P146" s="7" t="n"/>
-      <c r="Q146" s="6" t="n"/>
+      <c r="Q146" s="7" t="n"/>
       <c r="R146" s="6" t="n"/>
+      <c r="S146" s="6" t="n"/>
+      <c r="T146" s="6" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="6" t="n"/>
@@ -3559,8 +3865,10 @@
       <c r="N147" s="7" t="n"/>
       <c r="O147" s="7" t="n"/>
       <c r="P147" s="7" t="n"/>
-      <c r="Q147" s="6" t="n"/>
+      <c r="Q147" s="7" t="n"/>
       <c r="R147" s="6" t="n"/>
+      <c r="S147" s="6" t="n"/>
+      <c r="T147" s="6" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="6" t="n"/>
@@ -3579,8 +3887,10 @@
       <c r="N148" s="7" t="n"/>
       <c r="O148" s="7" t="n"/>
       <c r="P148" s="7" t="n"/>
-      <c r="Q148" s="6" t="n"/>
+      <c r="Q148" s="7" t="n"/>
       <c r="R148" s="6" t="n"/>
+      <c r="S148" s="6" t="n"/>
+      <c r="T148" s="6" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="6" t="n"/>
@@ -3599,8 +3909,10 @@
       <c r="N149" s="7" t="n"/>
       <c r="O149" s="7" t="n"/>
       <c r="P149" s="7" t="n"/>
-      <c r="Q149" s="6" t="n"/>
+      <c r="Q149" s="7" t="n"/>
       <c r="R149" s="6" t="n"/>
+      <c r="S149" s="6" t="n"/>
+      <c r="T149" s="6" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="6" t="n"/>
@@ -3619,8 +3931,10 @@
       <c r="N150" s="7" t="n"/>
       <c r="O150" s="7" t="n"/>
       <c r="P150" s="7" t="n"/>
-      <c r="Q150" s="6" t="n"/>
+      <c r="Q150" s="7" t="n"/>
       <c r="R150" s="6" t="n"/>
+      <c r="S150" s="6" t="n"/>
+      <c r="T150" s="6" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="6" t="n"/>
@@ -3639,8 +3953,10 @@
       <c r="N151" s="7" t="n"/>
       <c r="O151" s="7" t="n"/>
       <c r="P151" s="7" t="n"/>
-      <c r="Q151" s="6" t="n"/>
+      <c r="Q151" s="7" t="n"/>
       <c r="R151" s="6" t="n"/>
+      <c r="S151" s="6" t="n"/>
+      <c r="T151" s="6" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="6" t="n"/>
@@ -3659,8 +3975,10 @@
       <c r="N152" s="7" t="n"/>
       <c r="O152" s="7" t="n"/>
       <c r="P152" s="7" t="n"/>
-      <c r="Q152" s="6" t="n"/>
+      <c r="Q152" s="7" t="n"/>
       <c r="R152" s="6" t="n"/>
+      <c r="S152" s="6" t="n"/>
+      <c r="T152" s="6" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="6" t="n"/>
@@ -3679,8 +3997,10 @@
       <c r="N153" s="7" t="n"/>
       <c r="O153" s="7" t="n"/>
       <c r="P153" s="7" t="n"/>
-      <c r="Q153" s="6" t="n"/>
+      <c r="Q153" s="7" t="n"/>
       <c r="R153" s="6" t="n"/>
+      <c r="S153" s="6" t="n"/>
+      <c r="T153" s="6" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="6" t="n"/>
@@ -3699,8 +4019,10 @@
       <c r="N154" s="7" t="n"/>
       <c r="O154" s="7" t="n"/>
       <c r="P154" s="7" t="n"/>
-      <c r="Q154" s="6" t="n"/>
+      <c r="Q154" s="7" t="n"/>
       <c r="R154" s="6" t="n"/>
+      <c r="S154" s="6" t="n"/>
+      <c r="T154" s="6" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="6" t="n"/>
@@ -3719,8 +4041,10 @@
       <c r="N155" s="7" t="n"/>
       <c r="O155" s="7" t="n"/>
       <c r="P155" s="7" t="n"/>
-      <c r="Q155" s="6" t="n"/>
+      <c r="Q155" s="7" t="n"/>
       <c r="R155" s="6" t="n"/>
+      <c r="S155" s="6" t="n"/>
+      <c r="T155" s="6" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="6" t="n"/>
@@ -3739,8 +4063,10 @@
       <c r="N156" s="7" t="n"/>
       <c r="O156" s="7" t="n"/>
       <c r="P156" s="7" t="n"/>
-      <c r="Q156" s="6" t="n"/>
+      <c r="Q156" s="7" t="n"/>
       <c r="R156" s="6" t="n"/>
+      <c r="S156" s="6" t="n"/>
+      <c r="T156" s="6" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="6" t="n"/>
@@ -3759,8 +4085,10 @@
       <c r="N157" s="7" t="n"/>
       <c r="O157" s="7" t="n"/>
       <c r="P157" s="7" t="n"/>
-      <c r="Q157" s="6" t="n"/>
+      <c r="Q157" s="7" t="n"/>
       <c r="R157" s="6" t="n"/>
+      <c r="S157" s="6" t="n"/>
+      <c r="T157" s="6" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="6" t="n"/>
@@ -3779,8 +4107,10 @@
       <c r="N158" s="7" t="n"/>
       <c r="O158" s="7" t="n"/>
       <c r="P158" s="7" t="n"/>
-      <c r="Q158" s="6" t="n"/>
+      <c r="Q158" s="7" t="n"/>
       <c r="R158" s="6" t="n"/>
+      <c r="S158" s="6" t="n"/>
+      <c r="T158" s="6" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="6" t="n"/>
@@ -3799,8 +4129,10 @@
       <c r="N159" s="7" t="n"/>
       <c r="O159" s="7" t="n"/>
       <c r="P159" s="7" t="n"/>
-      <c r="Q159" s="6" t="n"/>
+      <c r="Q159" s="7" t="n"/>
       <c r="R159" s="6" t="n"/>
+      <c r="S159" s="6" t="n"/>
+      <c r="T159" s="6" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="6" t="n"/>
@@ -3819,8 +4151,10 @@
       <c r="N160" s="7" t="n"/>
       <c r="O160" s="7" t="n"/>
       <c r="P160" s="7" t="n"/>
-      <c r="Q160" s="6" t="n"/>
+      <c r="Q160" s="7" t="n"/>
       <c r="R160" s="6" t="n"/>
+      <c r="S160" s="6" t="n"/>
+      <c r="T160" s="6" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="6" t="n"/>
@@ -3839,8 +4173,10 @@
       <c r="N161" s="7" t="n"/>
       <c r="O161" s="7" t="n"/>
       <c r="P161" s="7" t="n"/>
-      <c r="Q161" s="6" t="n"/>
+      <c r="Q161" s="7" t="n"/>
       <c r="R161" s="6" t="n"/>
+      <c r="S161" s="6" t="n"/>
+      <c r="T161" s="6" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="6" t="n"/>
@@ -3859,8 +4195,10 @@
       <c r="N162" s="7" t="n"/>
       <c r="O162" s="7" t="n"/>
       <c r="P162" s="7" t="n"/>
-      <c r="Q162" s="6" t="n"/>
+      <c r="Q162" s="7" t="n"/>
       <c r="R162" s="6" t="n"/>
+      <c r="S162" s="6" t="n"/>
+      <c r="T162" s="6" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="6" t="n"/>
@@ -3879,8 +4217,10 @@
       <c r="N163" s="7" t="n"/>
       <c r="O163" s="7" t="n"/>
       <c r="P163" s="7" t="n"/>
-      <c r="Q163" s="6" t="n"/>
+      <c r="Q163" s="7" t="n"/>
       <c r="R163" s="6" t="n"/>
+      <c r="S163" s="6" t="n"/>
+      <c r="T163" s="6" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="6" t="n"/>
@@ -3899,8 +4239,10 @@
       <c r="N164" s="7" t="n"/>
       <c r="O164" s="7" t="n"/>
       <c r="P164" s="7" t="n"/>
-      <c r="Q164" s="6" t="n"/>
+      <c r="Q164" s="7" t="n"/>
       <c r="R164" s="6" t="n"/>
+      <c r="S164" s="6" t="n"/>
+      <c r="T164" s="6" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="6" t="n"/>
@@ -3919,8 +4261,10 @@
       <c r="N165" s="7" t="n"/>
       <c r="O165" s="7" t="n"/>
       <c r="P165" s="7" t="n"/>
-      <c r="Q165" s="6" t="n"/>
+      <c r="Q165" s="7" t="n"/>
       <c r="R165" s="6" t="n"/>
+      <c r="S165" s="6" t="n"/>
+      <c r="T165" s="6" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="6" t="n"/>
@@ -3939,8 +4283,10 @@
       <c r="N166" s="7" t="n"/>
       <c r="O166" s="7" t="n"/>
       <c r="P166" s="7" t="n"/>
-      <c r="Q166" s="6" t="n"/>
+      <c r="Q166" s="7" t="n"/>
       <c r="R166" s="6" t="n"/>
+      <c r="S166" s="6" t="n"/>
+      <c r="T166" s="6" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="6" t="n"/>
@@ -3959,8 +4305,10 @@
       <c r="N167" s="7" t="n"/>
       <c r="O167" s="7" t="n"/>
       <c r="P167" s="7" t="n"/>
-      <c r="Q167" s="6" t="n"/>
+      <c r="Q167" s="7" t="n"/>
       <c r="R167" s="6" t="n"/>
+      <c r="S167" s="6" t="n"/>
+      <c r="T167" s="6" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="6" t="n"/>
@@ -3979,8 +4327,10 @@
       <c r="N168" s="7" t="n"/>
       <c r="O168" s="7" t="n"/>
       <c r="P168" s="7" t="n"/>
-      <c r="Q168" s="6" t="n"/>
+      <c r="Q168" s="7" t="n"/>
       <c r="R168" s="6" t="n"/>
+      <c r="S168" s="6" t="n"/>
+      <c r="T168" s="6" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="6" t="n"/>
@@ -3999,8 +4349,10 @@
       <c r="N169" s="7" t="n"/>
       <c r="O169" s="7" t="n"/>
       <c r="P169" s="7" t="n"/>
-      <c r="Q169" s="6" t="n"/>
+      <c r="Q169" s="7" t="n"/>
       <c r="R169" s="6" t="n"/>
+      <c r="S169" s="6" t="n"/>
+      <c r="T169" s="6" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="6" t="n"/>
@@ -4019,8 +4371,10 @@
       <c r="N170" s="7" t="n"/>
       <c r="O170" s="7" t="n"/>
       <c r="P170" s="7" t="n"/>
-      <c r="Q170" s="6" t="n"/>
+      <c r="Q170" s="7" t="n"/>
       <c r="R170" s="6" t="n"/>
+      <c r="S170" s="6" t="n"/>
+      <c r="T170" s="6" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="6" t="n"/>
@@ -4039,8 +4393,10 @@
       <c r="N171" s="7" t="n"/>
       <c r="O171" s="7" t="n"/>
       <c r="P171" s="7" t="n"/>
-      <c r="Q171" s="6" t="n"/>
+      <c r="Q171" s="7" t="n"/>
       <c r="R171" s="6" t="n"/>
+      <c r="S171" s="6" t="n"/>
+      <c r="T171" s="6" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="6" t="n"/>
@@ -4059,8 +4415,10 @@
       <c r="N172" s="7" t="n"/>
       <c r="O172" s="7" t="n"/>
       <c r="P172" s="7" t="n"/>
-      <c r="Q172" s="6" t="n"/>
+      <c r="Q172" s="7" t="n"/>
       <c r="R172" s="6" t="n"/>
+      <c r="S172" s="6" t="n"/>
+      <c r="T172" s="6" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="6" t="n"/>
@@ -4079,8 +4437,10 @@
       <c r="N173" s="7" t="n"/>
       <c r="O173" s="7" t="n"/>
       <c r="P173" s="7" t="n"/>
-      <c r="Q173" s="6" t="n"/>
+      <c r="Q173" s="7" t="n"/>
       <c r="R173" s="6" t="n"/>
+      <c r="S173" s="6" t="n"/>
+      <c r="T173" s="6" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="6" t="n"/>
@@ -4099,8 +4459,10 @@
       <c r="N174" s="7" t="n"/>
       <c r="O174" s="7" t="n"/>
       <c r="P174" s="7" t="n"/>
-      <c r="Q174" s="6" t="n"/>
+      <c r="Q174" s="7" t="n"/>
       <c r="R174" s="6" t="n"/>
+      <c r="S174" s="6" t="n"/>
+      <c r="T174" s="6" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="6" t="n"/>
@@ -4119,8 +4481,10 @@
       <c r="N175" s="7" t="n"/>
       <c r="O175" s="7" t="n"/>
       <c r="P175" s="7" t="n"/>
-      <c r="Q175" s="6" t="n"/>
+      <c r="Q175" s="7" t="n"/>
       <c r="R175" s="6" t="n"/>
+      <c r="S175" s="6" t="n"/>
+      <c r="T175" s="6" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="6" t="n"/>
@@ -4139,8 +4503,10 @@
       <c r="N176" s="7" t="n"/>
       <c r="O176" s="7" t="n"/>
       <c r="P176" s="7" t="n"/>
-      <c r="Q176" s="6" t="n"/>
+      <c r="Q176" s="7" t="n"/>
       <c r="R176" s="6" t="n"/>
+      <c r="S176" s="6" t="n"/>
+      <c r="T176" s="6" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="6" t="n"/>
@@ -4159,8 +4525,10 @@
       <c r="N177" s="7" t="n"/>
       <c r="O177" s="7" t="n"/>
       <c r="P177" s="7" t="n"/>
-      <c r="Q177" s="6" t="n"/>
+      <c r="Q177" s="7" t="n"/>
       <c r="R177" s="6" t="n"/>
+      <c r="S177" s="6" t="n"/>
+      <c r="T177" s="6" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="6" t="n"/>
@@ -4179,8 +4547,10 @@
       <c r="N178" s="7" t="n"/>
       <c r="O178" s="7" t="n"/>
       <c r="P178" s="7" t="n"/>
-      <c r="Q178" s="6" t="n"/>
+      <c r="Q178" s="7" t="n"/>
       <c r="R178" s="6" t="n"/>
+      <c r="S178" s="6" t="n"/>
+      <c r="T178" s="6" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="6" t="n"/>
@@ -4199,8 +4569,10 @@
       <c r="N179" s="7" t="n"/>
       <c r="O179" s="7" t="n"/>
       <c r="P179" s="7" t="n"/>
-      <c r="Q179" s="6" t="n"/>
+      <c r="Q179" s="7" t="n"/>
       <c r="R179" s="6" t="n"/>
+      <c r="S179" s="6" t="n"/>
+      <c r="T179" s="6" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="6" t="n"/>
@@ -4219,8 +4591,10 @@
       <c r="N180" s="7" t="n"/>
       <c r="O180" s="7" t="n"/>
       <c r="P180" s="7" t="n"/>
-      <c r="Q180" s="6" t="n"/>
+      <c r="Q180" s="7" t="n"/>
       <c r="R180" s="6" t="n"/>
+      <c r="S180" s="6" t="n"/>
+      <c r="T180" s="6" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="6" t="n"/>
@@ -4239,8 +4613,10 @@
       <c r="N181" s="7" t="n"/>
       <c r="O181" s="7" t="n"/>
       <c r="P181" s="7" t="n"/>
-      <c r="Q181" s="6" t="n"/>
+      <c r="Q181" s="7" t="n"/>
       <c r="R181" s="6" t="n"/>
+      <c r="S181" s="6" t="n"/>
+      <c r="T181" s="6" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="6" t="n"/>
@@ -4259,8 +4635,10 @@
       <c r="N182" s="7" t="n"/>
       <c r="O182" s="7" t="n"/>
       <c r="P182" s="7" t="n"/>
-      <c r="Q182" s="6" t="n"/>
+      <c r="Q182" s="7" t="n"/>
       <c r="R182" s="6" t="n"/>
+      <c r="S182" s="6" t="n"/>
+      <c r="T182" s="6" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="6" t="n"/>
@@ -4279,8 +4657,10 @@
       <c r="N183" s="7" t="n"/>
       <c r="O183" s="7" t="n"/>
       <c r="P183" s="7" t="n"/>
-      <c r="Q183" s="6" t="n"/>
+      <c r="Q183" s="7" t="n"/>
       <c r="R183" s="6" t="n"/>
+      <c r="S183" s="6" t="n"/>
+      <c r="T183" s="6" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="6" t="n"/>
@@ -4299,8 +4679,10 @@
       <c r="N184" s="7" t="n"/>
       <c r="O184" s="7" t="n"/>
       <c r="P184" s="7" t="n"/>
-      <c r="Q184" s="6" t="n"/>
+      <c r="Q184" s="7" t="n"/>
       <c r="R184" s="6" t="n"/>
+      <c r="S184" s="6" t="n"/>
+      <c r="T184" s="6" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="6" t="n"/>
@@ -4319,8 +4701,10 @@
       <c r="N185" s="7" t="n"/>
       <c r="O185" s="7" t="n"/>
       <c r="P185" s="7" t="n"/>
-      <c r="Q185" s="6" t="n"/>
+      <c r="Q185" s="7" t="n"/>
       <c r="R185" s="6" t="n"/>
+      <c r="S185" s="6" t="n"/>
+      <c r="T185" s="6" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="6" t="n"/>
@@ -4339,8 +4723,10 @@
       <c r="N186" s="7" t="n"/>
       <c r="O186" s="7" t="n"/>
       <c r="P186" s="7" t="n"/>
-      <c r="Q186" s="6" t="n"/>
+      <c r="Q186" s="7" t="n"/>
       <c r="R186" s="6" t="n"/>
+      <c r="S186" s="6" t="n"/>
+      <c r="T186" s="6" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="6" t="n"/>
@@ -4359,8 +4745,10 @@
       <c r="N187" s="7" t="n"/>
       <c r="O187" s="7" t="n"/>
       <c r="P187" s="7" t="n"/>
-      <c r="Q187" s="6" t="n"/>
+      <c r="Q187" s="7" t="n"/>
       <c r="R187" s="6" t="n"/>
+      <c r="S187" s="6" t="n"/>
+      <c r="T187" s="6" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="6" t="n"/>
@@ -4379,8 +4767,10 @@
       <c r="N188" s="7" t="n"/>
       <c r="O188" s="7" t="n"/>
       <c r="P188" s="7" t="n"/>
-      <c r="Q188" s="6" t="n"/>
+      <c r="Q188" s="7" t="n"/>
       <c r="R188" s="6" t="n"/>
+      <c r="S188" s="6" t="n"/>
+      <c r="T188" s="6" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="6" t="n"/>
@@ -4399,8 +4789,10 @@
       <c r="N189" s="7" t="n"/>
       <c r="O189" s="7" t="n"/>
       <c r="P189" s="7" t="n"/>
-      <c r="Q189" s="6" t="n"/>
+      <c r="Q189" s="7" t="n"/>
       <c r="R189" s="6" t="n"/>
+      <c r="S189" s="6" t="n"/>
+      <c r="T189" s="6" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="6" t="n"/>
@@ -4419,8 +4811,10 @@
       <c r="N190" s="7" t="n"/>
       <c r="O190" s="7" t="n"/>
       <c r="P190" s="7" t="n"/>
-      <c r="Q190" s="6" t="n"/>
+      <c r="Q190" s="7" t="n"/>
       <c r="R190" s="6" t="n"/>
+      <c r="S190" s="6" t="n"/>
+      <c r="T190" s="6" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="6" t="n"/>
@@ -4439,8 +4833,10 @@
       <c r="N191" s="7" t="n"/>
       <c r="O191" s="7" t="n"/>
       <c r="P191" s="7" t="n"/>
-      <c r="Q191" s="6" t="n"/>
+      <c r="Q191" s="7" t="n"/>
       <c r="R191" s="6" t="n"/>
+      <c r="S191" s="6" t="n"/>
+      <c r="T191" s="6" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="6" t="n"/>
@@ -4459,8 +4855,10 @@
       <c r="N192" s="7" t="n"/>
       <c r="O192" s="7" t="n"/>
       <c r="P192" s="7" t="n"/>
-      <c r="Q192" s="6" t="n"/>
+      <c r="Q192" s="7" t="n"/>
       <c r="R192" s="6" t="n"/>
+      <c r="S192" s="6" t="n"/>
+      <c r="T192" s="6" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="6" t="n"/>
@@ -4479,8 +4877,10 @@
       <c r="N193" s="7" t="n"/>
       <c r="O193" s="7" t="n"/>
       <c r="P193" s="7" t="n"/>
-      <c r="Q193" s="6" t="n"/>
+      <c r="Q193" s="7" t="n"/>
       <c r="R193" s="6" t="n"/>
+      <c r="S193" s="6" t="n"/>
+      <c r="T193" s="6" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="6" t="n"/>
@@ -4499,8 +4899,10 @@
       <c r="N194" s="7" t="n"/>
       <c r="O194" s="7" t="n"/>
       <c r="P194" s="7" t="n"/>
-      <c r="Q194" s="6" t="n"/>
+      <c r="Q194" s="7" t="n"/>
       <c r="R194" s="6" t="n"/>
+      <c r="S194" s="6" t="n"/>
+      <c r="T194" s="6" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="6" t="n"/>
@@ -4519,8 +4921,10 @@
       <c r="N195" s="7" t="n"/>
       <c r="O195" s="7" t="n"/>
       <c r="P195" s="7" t="n"/>
-      <c r="Q195" s="6" t="n"/>
+      <c r="Q195" s="7" t="n"/>
       <c r="R195" s="6" t="n"/>
+      <c r="S195" s="6" t="n"/>
+      <c r="T195" s="6" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="6" t="n"/>
@@ -4539,8 +4943,10 @@
       <c r="N196" s="7" t="n"/>
       <c r="O196" s="7" t="n"/>
       <c r="P196" s="7" t="n"/>
-      <c r="Q196" s="6" t="n"/>
+      <c r="Q196" s="7" t="n"/>
       <c r="R196" s="6" t="n"/>
+      <c r="S196" s="6" t="n"/>
+      <c r="T196" s="6" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="6" t="n"/>
@@ -4559,8 +4965,10 @@
       <c r="N197" s="7" t="n"/>
       <c r="O197" s="7" t="n"/>
       <c r="P197" s="7" t="n"/>
-      <c r="Q197" s="6" t="n"/>
+      <c r="Q197" s="7" t="n"/>
       <c r="R197" s="6" t="n"/>
+      <c r="S197" s="6" t="n"/>
+      <c r="T197" s="6" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="6" t="n"/>
@@ -4579,8 +4987,10 @@
       <c r="N198" s="7" t="n"/>
       <c r="O198" s="7" t="n"/>
       <c r="P198" s="7" t="n"/>
-      <c r="Q198" s="6" t="n"/>
+      <c r="Q198" s="7" t="n"/>
       <c r="R198" s="6" t="n"/>
+      <c r="S198" s="6" t="n"/>
+      <c r="T198" s="6" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="6" t="n"/>
@@ -4599,8 +5009,10 @@
       <c r="N199" s="7" t="n"/>
       <c r="O199" s="7" t="n"/>
       <c r="P199" s="7" t="n"/>
-      <c r="Q199" s="6" t="n"/>
+      <c r="Q199" s="7" t="n"/>
       <c r="R199" s="6" t="n"/>
+      <c r="S199" s="6" t="n"/>
+      <c r="T199" s="6" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="6" t="n"/>
@@ -4619,8 +5031,10 @@
       <c r="N200" s="7" t="n"/>
       <c r="O200" s="7" t="n"/>
       <c r="P200" s="7" t="n"/>
-      <c r="Q200" s="6" t="n"/>
+      <c r="Q200" s="7" t="n"/>
       <c r="R200" s="6" t="n"/>
+      <c r="S200" s="6" t="n"/>
+      <c r="T200" s="6" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="6" t="n"/>
@@ -4639,8 +5053,10 @@
       <c r="N201" s="7" t="n"/>
       <c r="O201" s="7" t="n"/>
       <c r="P201" s="7" t="n"/>
-      <c r="Q201" s="6" t="n"/>
+      <c r="Q201" s="7" t="n"/>
       <c r="R201" s="6" t="n"/>
+      <c r="S201" s="6" t="n"/>
+      <c r="T201" s="6" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="6" t="n"/>
@@ -4659,15 +5075,17 @@
       <c r="N202" s="7" t="n"/>
       <c r="O202" s="7" t="n"/>
       <c r="P202" s="7" t="n"/>
-      <c r="Q202" s="6" t="n"/>
+      <c r="Q202" s="7" t="n"/>
       <c r="R202" s="6" t="n"/>
+      <c r="S202" s="6" t="n"/>
+      <c r="T202" s="6" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="G3:G202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="構造" error="一覧から選んでください。表記が違うと取り込めません。" type="list">
       <formula1>"木造・合成樹脂造,木骨モルタル造,鉄骨造(骨格材3mm以下),鉄骨造(3mm超4mm以下),鉄骨造(4mm超),RC造"</formula1>
     </dataValidation>
-    <dataValidation sqref="R3:R202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="所得税率(%)" error="33 / 40 / 45 のいずれかを選んでください。" type="list">
+    <dataValidation sqref="T3:T202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="所得税率(%)" error="33 / 40 / 45 のいずれかを選んでください。" type="list">
       <formula1>"33,40,45"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4681,7 +5099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -4756,25 +5174,39 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>9. 写真はExcelでは扱いません。取り込んだあと、アプリの入力画面で1枚だけ追加してください。</t>
+          <t>9. 「登記費用」は登録免許税と司法書士報酬の合計です。初年度の経費として計算に入ります。空欄なら 0 です。</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr"/>
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>10. 「試算期間(年)」は節税効果を合計する年数です(1〜35)。空欄なら 15 年です。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
+          <t>11. 写真はExcelでは扱いません。取り込んだあと、アプリの入力画面で1枚だけ追加してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
           <t>入力し終えたら、アプリの一覧画面で「Excelから取り込み」を押してこのファイルを選びます。</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>列の意味で迷ったら docs/spec.md の第4章を参照してください。</t>
         </is>
